--- a/data/베이핑존.xlsx
+++ b/data/베이핑존.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86A6FC3-A91B-4DB8-96B9-D7166D177D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EADA6BC-7564-4140-A18D-E17FBA8BA5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{C3FB9D37-16CD-498F-BE3E-EB9B2A1AC5A0}"/>
+    <workbookView xWindow="9825" yWindow="405" windowWidth="29040" windowHeight="15480" xr2:uid="{C3FB9D37-16CD-498F-BE3E-EB9B2A1AC5A0}"/>
   </bookViews>
   <sheets>
     <sheet name="베이핑존" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>상품번호</t>
   </si>
@@ -251,13 +251,34 @@
   </si>
   <si>
     <t>미션 전자담배 킷 - 넵튠블루</t>
+  </si>
+  <si>
+    <t>더스페셜 더블그레이프 입호흡 30ml</t>
+  </si>
+  <si>
+    <t>더스페셜 더블포카리 입호흡 30ml</t>
+  </si>
+  <si>
+    <t>더스페셜 더블라임 입호흡 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 딸기밀크 입호흡 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 웰치스 입호흡 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 쿨체리 입호흡 30ml</t>
+  </si>
+  <si>
+    <t>쿨크러쉬 파인패션후르츠 입호흡 30ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +438,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -843,8 +871,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1222,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A842B7-70F4-401F-814E-E19F49BA1857}">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -1833,6 +1864,62 @@
         <v>76</v>
       </c>
     </row>
+    <row r="77" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>298</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>299</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>300</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>301</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>302</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>303</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>304</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
